--- a/consent_forms/019_wildlife_rehabilitation_intake_form--consent_forms.xlsx
+++ b/consent_forms/019_wildlife_rehabilitation_intake_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mammal',_'value':_1}</t>
+          <t>mammal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mammal', 'value': 1}</t>
+          <t>Mammal</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bird',_'value':_2}</t>
+          <t>bird</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bird', 'value': 2}</t>
+          <t>Bird</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'reptile',_'value':_3}</t>
+          <t>reptile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Reptile', 'value': 3}</t>
+          <t>Reptile</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rehabilitation',_'value':_1}</t>
+          <t>rehabilitation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rehabilitation', 'value': 1}</t>
+          <t>Rehabilitation</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'release',_'value':_2}</t>
+          <t>release</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Release', 'value': 2}</t>
+          <t>Release</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_3}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 3}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_1}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 1}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_2}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown',_'value':_3}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown', 'value': 3}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
